--- a/StructureDefinition-mii-lm-labor.xlsx
+++ b/StructureDefinition-mii-lm-labor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:43:45+00:00</t>
+    <t>2026-09-08T13:08:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-lm-labor.xlsx
+++ b/StructureDefinition-mii-lm-labor.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:08:25+00:00</t>
+    <t>2026-09-10T17:57:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
